--- a/GWD Data/PVC With Trench PRICE.xlsx
+++ b/GWD Data/PVC With Trench PRICE.xlsx
@@ -44,7 +44,7 @@
     <t>Label</t>
   </si>
   <si>
-    <t>Providing and fixing PVC pipes includings jointing of pipes with one step PVC solvent cement, trenching, refilling &amp; testing of joints complete as per direction of Engineer in Charge 15 mm dia 12Kfg/cm2 (50.18.9.1.1)</t>
+    <t>Providing and fixing PVC pipes including jointing of pipes with one step PVC solvent cement, trenching, refilling &amp; testing of joints complete as per direction of Engineer in Charge 15 mm dia 12Kfg/cm2 (50.18.9.1.1)</t>
   </si>
   <si>
     <t>Header Unit</t>
@@ -130,7 +130,7 @@
     <t>TOTAL (Labour)</t>
   </si>
   <si>
-    <t>Providing and fixing PVC pipes includings jointing of pipes with one step PVC solvent cement, trenching, refilling &amp; testing of joints complete as per direction of Engineer in Charge. 15 mm dia 10Kgf/cm2 (50.18.9.1.2)</t>
+    <t>Providing and fixing PVC pipes including jointing of pipes with one step PVC solvent cement, trenching, refilling &amp; testing of joints complete as per direction of Engineer in Charge. 15 mm dia 10Kgf/cm2 (50.18.9.1.2)</t>
   </si>
   <si>
     <t>Details of cost for 10 metres</t>
@@ -147,7 +147,7 @@
 Trenching and refilling etc</t>
   </si>
   <si>
-    <t>Providing and fixing PVC pipes includings jointing of pipes with one step PVC solvent cement, trenching, refilling &amp; testing of joints as per direction of Engineer in Charge.20 mm dia 12 Kgf/cm2 (50.18.9.2.1)</t>
+    <t>Providing and fixing PVC pipes including jointing of pipes with one step PVC solvent cement, trenching, refilling &amp; testing of joints as per direction of Engineer in Charge.20 mm dia 12 Kgf/cm2 (50.18.9.2.1)</t>
   </si>
   <si>
     <t>Details of cost for 10.00 meter</t>
@@ -160,7 +160,7 @@
 Add 15% for fittings and wastage etc. on (A)</t>
   </si>
   <si>
-    <t>Providing and fixing PVC pipes includings of pipes with one step PVC solvent cement, trenching, refilling &amp; testing of joints complete as per direction of Engineer in Charge. 20 mm dia 10 Kgf/cm2 (50.18.9.2.2)</t>
+    <t>Providing and fixing PVC pipes including of pipes with one step PVC solvent cement, trenching, refilling &amp; testing of joints complete as per direction of Engineer in Charge. 20 mm dia 10 Kgf/cm2 (50.18.9.2.2)</t>
   </si>
   <si>
     <t>Details of cost for 10 meter</t>
@@ -173,7 +173,7 @@
 Add 15% for fittings and wastage etc. on (A)</t>
   </si>
   <si>
-    <t>Providing and fixing PVC pipes includings jointing of pipes with one step PVC solvent cement, trenching, refilling &amp; testing of joints complete as per direction of Engineer in Charge 25 mm dia 12Kfg/cm2 (50.18.9.3.1)</t>
+    <t>Providing and fixing PVC pipes including jointing of pipes with one step PVC solvent cement, trenching, refilling &amp; testing of joints complete as per direction of Engineer in Charge 25 mm dia 12Kfg/cm2 (50.18.9.3.1)</t>
   </si>
   <si>
     <t>MR42</t>
@@ -196,7 +196,7 @@
 Add 15% for fittings and wastage etc. on (A)</t>
   </si>
   <si>
-    <t>Providing and fixing PVC pipes includings jointing of pipes with one step PVC solvent cement, trenching, refilling &amp; testing of joints complete as per direction of Engineer in Charge.32 mm dia 10.Kgf/cm2 (50.18.9.4.1)</t>
+    <t>Providing and fixing PVC pipes including jointing of pipes with one step PVC solvent cement, trenching, refilling &amp; testing of joints complete as per direction of Engineer in Charge.32 mm dia 10.Kgf/cm2 (50.18.9.4.1)</t>
   </si>
   <si>
     <t>Details of cost for 10 .00 metre.</t>
@@ -209,7 +209,7 @@
 Add 15% for fittings and wastage etc. on (A)</t>
   </si>
   <si>
-    <t>Providing and fixing PVC pipes includings joints of pipes with one step PVC solvent cement, trenching, refilling &amp; testing of joints complete as per direction of Engineer in Charge. 32 mm dia 6 Kgf/cm2 (50.18.9.4.2)</t>
+    <t>Providing and fixing PVC pipes including joints of pipes with one step PVC solvent cement, trenching, refilling &amp; testing of joints complete as per direction of Engineer in Charge. 32 mm dia 6 Kgf/cm2 (50.18.9.4.2)</t>
   </si>
   <si>
     <t>Details of cost for 10.00 metre</t>
@@ -222,7 +222,7 @@
 Add 15% for fittings and wastage etc. on (A)</t>
   </si>
   <si>
-    <t>Providing and fixing PVC pipes includings jointing of pipes with one step PVC solvent cement, trenching refilling &amp; testing of joints complete as per direction of Engineer in Charge 40 mm dia 10Kgf/cm2 (50.18.9.5.1)</t>
+    <t>Providing and fixing PVC pipes including jointing of pipes with one step PVC solvent cement, trenching refilling &amp; testing of joints complete as per direction of Engineer in Charge 40 mm dia 10Kgf/cm2 (50.18.9.5.1)</t>
   </si>
   <si>
     <t>MR46</t>
@@ -232,7 +232,7 @@
 Add 15% for fittings and wastage etc. on</t>
   </si>
   <si>
-    <t>Providing and fixing PVC pipes includings jointing of pipes with one step PVC solvent cement, trenching, refilling &amp; testing of joints compete as per direction of Engineer in Charge. 40 mm dia 6 Kgf/cm2 (50.18.9.5.2)</t>
+    <t>Providing and fixing PVC pipes including jointing of pipes with one step PVC solvent cement, trenching, refilling &amp; testing of joints compete as per direction of Engineer in Charge. 40 mm dia 6 Kgf/cm2 (50.18.9.5.2)</t>
   </si>
   <si>
     <t>MR47</t>
@@ -242,7 +242,7 @@
 Add 15% for fittings and wastage etc. on (A)</t>
   </si>
   <si>
-    <t>Providing and fixing PVC pipes includings jointing of pipes with one step PVC solvent cement, trenching, refilling &amp; testing of joints complete as per direction of Engineer in Charge. 50 mm dia 10Kgf/cm2 (50.18.9.6.1)</t>
+    <t>Providing and fixing PVC pipes including jointing of pipes with one step PVC solvent cement, trenching, refilling &amp; testing of joints complete as per direction of Engineer in Charge. 50 mm dia 10Kgf/cm2 (50.18.9.6.1)</t>
   </si>
   <si>
     <t>MR48</t>
@@ -252,7 +252,7 @@
 Add 15% for fittings and wastage etc. on</t>
   </si>
   <si>
-    <t>Providing and fixing PVC pipes includings jointing of pipes with one step PVC solvent cement, trenching, refilling &amp; testing of joints complete as per direction of Engineer in Charge. 50 mm dia 6 Kgf/cm2 (50.18.9.6.2)</t>
+    <t>Providing and fixing PVC pipes including jointing of pipes with one step PVC solvent cement, trenching, refilling &amp; testing of joints complete as per direction of Engineer in Charge. 50 mm dia 6 Kgf/cm2 (50.18.9.6.2)</t>
   </si>
   <si>
     <t>MR49</t>
@@ -262,7 +262,7 @@
 Add 15% for fittings and wastage etc. on (A)</t>
   </si>
   <si>
-    <t>Providing and fixing PVC pipes includings of pipes with one step PVC solvent cement, trenching refilling &amp; testing of joints complete as per direction of Engineer in Charge. 63 mm dia 6Kgf/cm2 (50.18.9.7.1)</t>
+    <t>Providing and fixing PVC pipes including of pipes with one step PVC solvent cement, trenching refilling &amp; testing of joints complete as per direction of Engineer in Charge. 63 mm dia 6Kgf/cm2 (50.18.9.7.1)</t>
   </si>
   <si>
     <t>MR50</t>
@@ -271,7 +271,7 @@
     <t>PVC pipe 63 mm outer dia . 6kgf/cm2</t>
   </si>
   <si>
-    <t>Providing and fixing PVC pipes includings jointing of pipes with one step PVC solvent cement, trenching, refilling &amp; testing of joints complete as per direction of Engineer in Charge.63 mm dia 4 Kgf/cm2 (50.18.9.7.2)</t>
+    <t>Providing and fixing PVC pipes including jointing of pipes with one step PVC solvent cement, trenching, refilling &amp; testing of joints complete as per direction of Engineer in Charge.63 mm dia 4 Kgf/cm2 (50.18.9.7.2)</t>
   </si>
   <si>
     <t>MR51</t>
@@ -281,7 +281,7 @@
 Add 5% for wastage etc. on (A)</t>
   </si>
   <si>
-    <t>Providing and fixing PVC pipes includings jointing of pipes with one step PVC solvent cement, trenching, refilling &amp; testing of joints complete as per direction of Engineer in Charge. 75 mm dia 6 Kgf/ cm2 50.18.9.8.1)</t>
+    <t>Providing and fixing PVC pipes including jointing of pipes with one step PVC solvent cement, trenching, refilling &amp; testing of joints complete as per direction of Engineer in Charge. 75 mm dia 6 Kgf/ cm2 50.18.9.8.1)</t>
   </si>
   <si>
     <t>MR52</t>
@@ -291,7 +291,7 @@
 Add 5% for wastage etc. on (A)</t>
   </si>
   <si>
-    <t>Providing and fixing PVC pipes includings of pipes with one step PVC solvent cement, trenching and refilling &amp; testing of joints complete as per direction of Engineer in Charge. 75 mm dia 4 Kgf/cm2 50.18.9.8.2)</t>
+    <t>Providing and fixing PVC pipes including of pipes with one step PVC solvent cement, trenching and refilling &amp; testing of joints complete as per direction of Engineer in Charge. 75 mm dia 4 Kgf/cm2 50.18.9.8.2)</t>
   </si>
   <si>
     <t>MR53</t>
@@ -301,7 +301,7 @@
 Add 5% for wastage etc. on (A)</t>
   </si>
   <si>
-    <t>Providing and fixing PVC pipes includings jointing of pipes with one step PVC solvent cement, trenching, refilling &amp; testing of Joints complete as per direction of engineer in charge.110 mm dia 6Kgf/cm2 (50.18.9.9.1)</t>
+    <t>Providing and fixing PVC pipes including jointing of pipes with one step PVC solvent cement, trenching, refilling &amp; testing of Joints complete as per direction of engineer in charge.110 mm dia 6Kgf/cm2 (50.18.9.9.1)</t>
   </si>
   <si>
     <t>Details of cost for 10. meter</t>
@@ -324,7 +324,7 @@
 Add 5% for wastage etc. on (A)</t>
   </si>
   <si>
-    <t>Providing and fixing PVC pipes includings jointing of pipes with one step pvc solvent cement, trenching , refilling &amp; testing of joints complete as per direction of Engineer in Charge. 150 mm dia 6 Kgf/cm2 (50.18.9.10.1)</t>
+    <t>Providing and fixing PVC pipes including jointing of pipes with one step pvc solvent cement, trenching , refilling &amp; testing of joints complete as per direction of Engineer in Charge. 150 mm dia 6 Kgf/cm2 (50.18.9.10.1)</t>
   </si>
   <si>
     <t>MR56</t>
@@ -961,7 +961,7 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{4DF8CFA3-7B65-411F-A0DA-4F7AA55CB9A6}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{08FA8FA0-CE25-44EC-9300-73C4D10BB9A6}">
   <dimension ref="A1:G570"/>
   <sheetFormatPr defaultRowHeight="12.75"/>
   <sheetData>

--- a/GWD Data/PVC With Trench PRICE.xlsx
+++ b/GWD Data/PVC With Trench PRICE.xlsx
@@ -44,7 +44,7 @@
     <t>Label</t>
   </si>
   <si>
-    <t>Providing and fixing PVC pipes including jointing of pipes with one step PVC solvent cement, trenching, refilling &amp; testing of joints complete as per direction of Engineer in Charge 15 mm dia 12Kfg/cm2 (50.18.9.1.1)</t>
+    <t>Providing and fixing PVC pipes including jointing of pipes with one step PVC solvent cement, trenching, refilling &amp; testing of joints complete as per direction of Engineer in Charge 15 mm dia 12kgf/cm2 (50.18.9.1.1)</t>
   </si>
   <si>
     <t>Header Unit</t>
@@ -173,7 +173,7 @@
 Add 15% for fittings and wastage etc. on (A)</t>
   </si>
   <si>
-    <t>Providing and fixing PVC pipes including jointing of pipes with one step PVC solvent cement, trenching, refilling &amp; testing of joints complete as per direction of Engineer in Charge 25 mm dia 12Kfg/cm2 (50.18.9.3.1)</t>
+    <t>Providing and fixing PVC pipes including jointing of pipes with one step PVC solvent cement, trenching, refilling &amp; testing of joints complete as per direction of Engineer in Charge 25 mm dia 12kgf/cm2 (50.18.9.3.1)</t>
   </si>
   <si>
     <t>MR42</t>
@@ -961,7 +961,7 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{08FA8FA0-CE25-44EC-9300-73C4D10BB9A6}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{643ADB76-5C53-4646-851D-C5DA69EBB9A6}">
   <dimension ref="A1:G570"/>
   <sheetFormatPr defaultRowHeight="12.75"/>
   <sheetData>
